--- a/backend/data/timetable.xlsx
+++ b/backend/data/timetable.xlsx
@@ -2016,12 +2016,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Aarti Sharma</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Kavita Patel</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>KP</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Amit Desai</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>AD</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Sneha Shah</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>SS</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Vijay Patel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>VP</t>
         </is>
       </c>
     </row>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Rohan Shah</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>RS</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Pooja Desai</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>PD</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Manish Mehta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>MM</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Priya Desai</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PD</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Hardik Joshi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>HJ</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Pooja Desai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>PD</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Aarti Sharma</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Hardik Joshi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HJ</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Sameer Verma</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SV</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Hardik Joshi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>HJ</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Aarti Sharma</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Meera Nair</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Neha Gupta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Meera Nair</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Sameer Verma</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SV</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Kavita Patel</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>KP</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Hardik Joshi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>HJ</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Meera Nair</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Neha Gupta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3104,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Sameer Verma</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SV</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Prof. Kavita Patel</t>
+          <t>Prof. Meera Nair</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KP</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Neha Gupta</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Prof. Rohan Shah</t>
+          <t>Prof. Arjun Mehta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Prof. Arjun Mehta</t>
+          <t>Prof. Sameer Verma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>SV</t>
         </is>
       </c>
     </row>
@@ -3328,12 +3328,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Prof. Priya Desai</t>
+          <t>Prof. Meera Nair</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
